--- a/数学群_20260829.xlsx
+++ b/数学群_20260829.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huil\checkin\WeChatTextExport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luhui\Python\checkin_v2\WeChatTextExport\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9E7B3523EB38D2300B343725318AF8C30AB88EFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17200"/>
+    <workbookView xWindow="16890" yWindow="50" windowWidth="19720" windowHeight="20950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,14 +50,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -72,345 +67,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -433,319 +105,33 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1023,22 +409,22 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.91666666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.9140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2">
         <f>SUM(B3:B10000)</f>
@@ -1047,7 +433,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1061,12 +447,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>29101</v>
       </c>
       <c r="B3" s="3">
-        <f t="shared" ref="B3:B52" si="0">C3+D3</f>
+        <f t="shared" ref="B3:B34" si="0">C3+D3</f>
         <v>25</v>
       </c>
       <c r="C3" s="2">
@@ -1076,7 +462,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>29102</v>
       </c>
@@ -1091,7 +477,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>29103</v>
       </c>
@@ -1106,7 +492,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>29104</v>
       </c>
@@ -1121,7 +507,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>29105</v>
       </c>
@@ -1136,7 +522,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>29106</v>
       </c>
@@ -1151,7 +537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>29107</v>
       </c>
@@ -1166,7 +552,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>29108</v>
       </c>
@@ -1181,7 +567,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>29109</v>
       </c>
@@ -1196,7 +582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>29110</v>
       </c>
@@ -1211,7 +597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>29111</v>
       </c>
@@ -1226,7 +612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>29112</v>
       </c>
@@ -1241,7 +627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>29113</v>
       </c>
@@ -1256,7 +642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>29114</v>
       </c>
@@ -1271,7 +657,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>29115</v>
       </c>
@@ -1286,7 +672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>29116</v>
       </c>
@@ -1301,7 +687,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>29117</v>
       </c>
@@ -1316,7 +702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>29118</v>
       </c>
@@ -1331,7 +717,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>29151</v>
       </c>
@@ -1346,7 +732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>29152</v>
       </c>
@@ -1361,7 +747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>29153</v>
       </c>
@@ -1376,7 +762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>29154</v>
       </c>
@@ -1391,7 +777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>29155</v>
       </c>
@@ -1406,7 +792,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>29156</v>
       </c>
@@ -1421,7 +807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>29157</v>
       </c>
@@ -1436,7 +822,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>29158</v>
       </c>
@@ -1451,7 +837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>29159</v>
       </c>
@@ -1466,7 +852,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29160</v>
       </c>
@@ -1481,7 +867,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>29161</v>
       </c>
@@ -1496,7 +882,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>29162</v>
       </c>
@@ -1511,7 +897,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>29163</v>
       </c>
@@ -1526,7 +912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>29164</v>
       </c>
@@ -1541,12 +927,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>29165</v>
       </c>
       <c r="B35" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B35:B66" si="1">C35+D35</f>
         <v>23</v>
       </c>
       <c r="C35" s="2">
@@ -1556,12 +942,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>29166</v>
       </c>
       <c r="B36" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="C36" s="2">
@@ -1571,12 +957,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>29167</v>
       </c>
       <c r="B37" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C37" s="2">
@@ -1586,12 +972,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>29168</v>
       </c>
       <c r="B38" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="C38" s="2">
@@ -1601,12 +987,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>29169</v>
       </c>
       <c r="B39" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="C39" s="2">
@@ -1616,12 +1002,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>29170</v>
       </c>
       <c r="B40" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="C40" s="2">
@@ -1631,12 +1017,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>29171</v>
       </c>
       <c r="B41" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C41" s="2">
@@ -1646,12 +1032,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>29172</v>
       </c>
       <c r="B42" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C42" s="2">
@@ -1661,12 +1047,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>29173</v>
       </c>
       <c r="B43" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="C43" s="2">
@@ -1676,12 +1062,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>29174</v>
       </c>
       <c r="B44" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C44" s="2">
@@ -1691,12 +1077,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>29175</v>
       </c>
       <c r="B45" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="C45" s="2">
@@ -1706,12 +1092,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>29176</v>
       </c>
       <c r="B46" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C46" s="2">
@@ -1721,12 +1107,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>29177</v>
       </c>
       <c r="B47" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="C47" s="2">
@@ -1736,12 +1122,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>29178</v>
       </c>
       <c r="B48" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="C48" s="2">
@@ -1751,12 +1137,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>29179</v>
       </c>
       <c r="B49" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="C49" s="2">
@@ -1766,12 +1152,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>29180</v>
       </c>
       <c r="B50" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C50" s="2">
@@ -1781,12 +1167,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>29181</v>
       </c>
       <c r="B51" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C51" s="2">
@@ -1796,12 +1182,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>29182</v>
       </c>
       <c r="B52" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C52" s="2">
@@ -1812,7 +1198,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/数学群_20260829.xlsx
+++ b/数学群_20260829.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luhui\Python\checkin_v2\WeChatTextExport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_9E7B3523EB38D2300B343725318AF8C30AB88EFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9E7B3523EB38D2300B343732F18FE7B10AB88EFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16890" yWindow="50" windowWidth="19720" windowHeight="20950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
